--- a/docs/demo-data/GNDEC/GNDEC_5_CE.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_5_CE.xlsx
@@ -904,7 +904,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dr. Gagandeep Bansal</t>
+          <t>Prof. Gagandeep Bansal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Er. Ritika Bains</t>
+          <t>Dr. Ritika Bains</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dr. Sanjeev Brar</t>
+          <t>Prof. Sanjeev Brar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Er. Deepika Sethi</t>
+          <t>Prof. Deepika Sethi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dr. Gagandeep Bansal</t>
+          <t>Prof. Gagandeep Bansal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1594,7 +1594,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Er. Ritika Bains</t>
+          <t>Dr. Ritika Bains</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dr. Sanjeev Brar</t>
+          <t>Prof. Sanjeev Brar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Er. Deepika Sethi</t>
+          <t>Prof. Deepika Sethi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1864,7 +1864,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1954,7 +1954,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Er. Deepika Sethi</t>
+          <t>Prof. Deepika Sethi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dr. Sanjeev Brar</t>
+          <t>Prof. Sanjeev Brar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Er. Deepika Sethi</t>
+          <t>Prof. Deepika Sethi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dr. Sanjeev Brar</t>
+          <t>Prof. Sanjeev Brar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2029,7 +2029,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dr. Sanjeev Brar</t>
+          <t>Prof. Sanjeev Brar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Er. Navneet Ahluwalia</t>
+          <t>Dr. Navneet Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Er. Simranjit Randhawa</t>
+          <t>Prof. Simranjit Randhawa</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Er. Simranjit Randhawa</t>
+          <t>Prof. Simranjit Randhawa</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Er. Simranjit Randhawa</t>
+          <t>Prof. Simranjit Randhawa</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Er. Ravneet Mittal</t>
+          <t>Dr. Ravneet Mittal</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Er. Ravneet Mittal</t>
+          <t>Dr. Ravneet Mittal</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Er. Ravneet Mittal</t>
+          <t>Dr. Ravneet Mittal</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Er. Manveer Khanna</t>
+          <t>Prof. Manveer Khanna</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Toor</t>
+          <t>Dr. Prabhjot Toor</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Toor</t>
+          <t>Dr. Prabhjot Toor</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Toor</t>
+          <t>Dr. Prabhjot Toor</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prof. Sanjeev Dhaliwal</t>
+          <t>Dr. Sanjeev Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prof. Sanjeev Dhaliwal</t>
+          <t>Dr. Sanjeev Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Er. Aman Bains</t>
+          <t>Dr. Aman Bains</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dr. Nidhi Brar</t>
+          <t>Prof. Nidhi Brar</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Er. Ishpreet Bhalla</t>
+          <t>Dr. Ishpreet Bhalla</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dr. Gagandeep Bansal</t>
+          <t>Prof. Gagandeep Bansal</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dr. Gagandeep Bansal</t>
+          <t>Prof. Gagandeep Bansal</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prof. Komal Dhaliwal</t>
+          <t>Dr. Komal Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Er. Anupam Gill</t>
+          <t>Prof. Anupam Gill</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Er. Ritika Bains</t>
+          <t>Dr. Ritika Bains</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dr. Sanjeev Brar</t>
+          <t>Prof. Sanjeev Brar</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Prof. Meenu Chopra</t>
+          <t>Dr. Meenu Chopra</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Er. Deepika Sethi</t>
+          <t>Prof. Deepika Sethi</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Gurleen Bansal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Jashan Jain</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Fatehbir Gupta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Prabhleen Saini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Diya Verma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Meher Kapoor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Sahil Pannu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Aditi Dhillon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Ekamjot Rana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Avneet Mehta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muskan Sandhu</t>
+          <t>Manjot Aulakh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Noor Sidhu</t>
+          <t>Arjun Gupta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hargun Chawla</t>
+          <t>Manav Saini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sukhmani Aulakh</t>
+          <t>Riya Verma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ishaan Rana</t>
+          <t>Zoya Kapoor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nikita Pannu</t>
+          <t>Arshdeep Pannu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Simran Verma</t>
+          <t>Yuvraj Dhillon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Gupta</t>
+          <t>Lovepreet Rana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mehakpreet Bansal</t>
+          <t>Ananya Mehta</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gurnoor Grewal</t>
+          <t>Kavya Aulakh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajbir Bedi</t>
+          <t>Rahul Kaur</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harleen Thind</t>
+          <t>Vansh Chawla</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Navjot Goyal</t>
+          <t>Sneha Gill</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sanya Malhi</t>
+          <t>Taranpreet Sidhu</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gurleen Gill</t>
+          <t>Khushi Malhi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jashan Kaur</t>
+          <t>Aarav Sandhu</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fatehbir Mehta</t>
+          <t>Kabir Goyal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prabhleen Dhillon</t>
+          <t>Priya Arora</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diya Kapoor</t>
+          <t>Uday Thind</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Meher Saini</t>
+          <t>Rohan Singh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sahil Jain</t>
+          <t>Sehaj Bedi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aditi Bhatia</t>
+          <t>Japneet Sharma</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ekamjot Sharma</t>
+          <t>Vihaan Grewal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avneet Singh</t>
+          <t>Jasleen Bhatia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manjot Arora</t>
+          <t>Pranav Bansal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arjun Sandhu</t>
+          <t>Tanvi Jain</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manav Sidhu</t>
+          <t>Rohan Arora</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Riya Chawla</t>
+          <t>Sehaj Thind</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zoya Aulakh</t>
+          <t>Japneet Singh</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arshdeep Rana</t>
+          <t>Vihaan Bedi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yuvraj Pannu</t>
+          <t>Jasleen Sharma</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lovepreet Verma</t>
+          <t>Pranav Grewal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ananya Gupta</t>
+          <t>Tanvi Bhatia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kavya Bansal</t>
+          <t>Muskan Bansal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rahul Grewal</t>
+          <t>Noor Jain</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vansh Bedi</t>
+          <t>Hargun Gupta</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sneha Thind</t>
+          <t>Sukhmani Saini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Taranpreet Goyal</t>
+          <t>Ishaan Verma</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Khushi Malhi</t>
+          <t>Nikita Kapoor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aarav Gill</t>
+          <t>Simran Pannu</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Karan Dhillon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Mehakpreet Rana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Gurnoor Mehta</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Rajbir Aulakh</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Harleen Kaur</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Navjot Chawla</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Sanya Gill</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Gurleen Sidhu</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Jashan Malhi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Fatehbir Sandhu</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Prabhleen Goyal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Diya Mehta</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Meher Aulakh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Sahil Kaur</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Aditi Chawla</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Ekamjot Gill</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Avneet Sidhu</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Manjot Malhi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Arjun Sandhu</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Manav Goyal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Riya Arora</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Zoya Thind</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Yuvraj Bedi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Lovepreet Sharma</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Ananya Grewal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Kavya Bhatia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Rahul Bansal</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Vansh Jain</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Sneha Gupta</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Taranpreet Saini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Khushi Verma</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Aarav Kapoor</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Kabir Pannu</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Priya Dhillon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Uday Rana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Sneha Bansal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Taranpreet Jain</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Khushi Gupta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Aarav Saini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Kabir Verma</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Priya Kapoor</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Uday Pannu</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Rohan Dhillon</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Sehaj Rana</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Japneet Mehta</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Vihaan Aulakh</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Jasleen Kaur</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Pranav Chawla</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Tanvi Gill</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Muskan Sidhu</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Noor Malhi</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Hargun Sandhu</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Sukhmani Goyal</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Ishaan Arora</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Nikita Thind</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Simran Singh</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Karan Bedi</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Mehakpreet Sharma</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Gurnoor Grewal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Rajbir Bhatia</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Harleen Sandhu</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Navjot Goyal</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Sanya Arora</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Gurleen Thind</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Jashan Singh</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Fatehbir Bedi</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Prabhleen Sharma</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Diya Grewal</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Meher Bhatia</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Sahil Bansal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Aditi Jain</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Ekamjot Gupta</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Avneet Saini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Manjot Verma</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Arjun Kapoor</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Manav Pannu</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Riya Dhillon</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Zoya Rana</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Arshdeep Mehta</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Yuvraj Aulakh</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Lovepreet Kaur</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Ananya Chawla</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Kavya Gill</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Rahul Sidhu</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Vansh Malhi</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Arshdeep Dhillon</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Yuvraj Rana</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Lovepreet Mehta</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Ananya Aulakh</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Kavya Kaur</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Rahul Chawla</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Vansh Gill</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Sneha Sidhu</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Taranpreet Malhi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Khushi Sandhu</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Aarav Goyal</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Kabir Arora</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Priya Thind</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Uday Singh</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Rohan Bedi</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Sehaj Sharma</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Japneet Grewal</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Vihaan Bhatia</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Jasleen Bansal</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Pranav Jain</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Tanvi Gupta</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Muskan Saini</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Noor Verma</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Hargun Kapoor</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Sukhmani Pannu</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Ishaan Grewal</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Nikita Bhatia</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Simran Bansal</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Karan Jain</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Mehakpreet Gupta</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Gurnoor Saini</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Rajbir Verma</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Harleen Kapoor</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Navjot Pannu</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Sanya Dhillon</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Gurleen Rana</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Jashan Mehta</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Fatehbir Aulakh</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Prabhleen Kaur</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Diya Chawla</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Meher Gill</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Sahil Sidhu</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Aditi Malhi</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Ekamjot Sandhu</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Avneet Goyal</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Manjot Arora</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Arjun Thind</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Manav Singh</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Riya Bedi</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Zoya Sharma</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Ekamjot Sidhu</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Avneet Malhi</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Manjot Sandhu</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Arjun Goyal</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Manav Arora</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Riya Thind</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Zoya Singh</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Arshdeep Bedi</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Yuvraj Sharma</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Lovepreet Grewal</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Ananya Bhatia</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Kavya Bansal</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Rahul Jain</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Vansh Gupta</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Sneha Saini</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Taranpreet Verma</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Khushi Kapoor</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Aarav Pannu</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Kabir Dhillon</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Priya Rana</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Uday Mehta</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Rohan Aulakh</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Sehaj Kaur</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Japneet Chawla</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Vihaan Gill</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Jasleen Kapoor</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Pranav Pannu</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Tanvi Dhillon</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Muskan Rana</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Noor Mehta</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Hargun Aulakh</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Sukhmani Kaur</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Ishaan Chawla</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Nikita Gill</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Simran Sidhu</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Karan Malhi</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Mehakpreet Sandhu</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Gurnoor Goyal</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Rajbir Arora</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Harleen Thind</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Navjot Singh</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Sanya Bedi</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Gurleen Sharma</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Jashan Grewal</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Fatehbir Bhatia</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Prabhleen Bansal</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Diya Jain</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Meher Gupta</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Sahil Saini</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Aditi Verma</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Jashan Bedi</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Fatehbir Sharma</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Prabhleen Grewal</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Diya Bhatia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Meher Bansal</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Sahil Jain</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Aditi Gupta</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Ekamjot Saini</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Avneet Verma</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Manjot Kapoor</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Arjun Pannu</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Manav Dhillon</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Riya Rana</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Zoya Mehta</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Arshdeep Aulakh</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Yuvraj Kaur</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Lovepreet Chawla</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Ananya Gill</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Kavya Sidhu</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Rahul Malhi</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Vansh Sandhu</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Sneha Goyal</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Taranpreet Arora</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Khushi Thind</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Aarav Singh</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Kabir Chawla</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Priya Gill</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Uday Sidhu</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Rohan Malhi</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Sehaj Sandhu</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Japneet Goyal</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Vihaan Arora</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Jasleen Thind</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Pranav Singh</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Tanvi Bedi</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Muskan Sharma</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Noor Grewal</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Hargun Bhatia</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Sukhmani Bansal</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Ishaan Jain</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Nikita Gupta</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Simran Saini</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Karan Verma</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Mehakpreet Kapoor</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Gurnoor Pannu</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Rajbir Dhillon</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Harleen Rana</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Navjot Mehta</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Sanya Aulakh</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Gurleen Kaur</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Mehakpreet Saini</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Gurnoor Verma</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Rajbir Kapoor</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Harleen Pannu</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Navjot Dhillon</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Sanya Rana</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Gurleen Mehta</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Jashan Aulakh</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Fatehbir Kaur</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Prabhleen Chawla</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Diya Gill</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Meher Sidhu</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">

--- a/docs/demo-data/GNDEC/GNDEC_5_CE.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_5_CE.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -472,178 +472,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>then CSE, IT, ME and CE. Shared halls, the JPAL hour and the final-year CSE elective are set up by</t>
+          <t>then CSE, IT, ME and CE. Its file also has the lecture theatres, drawing halls and workshops of</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>the College Admin (they are already in the built-in GNDEC demo college).</t>
+          <t>first year. Not in the files: the JPAL hour and the final-year CSE elective (they need a student list</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>per group; they are in the built-in GNDEC demo college).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Timetabl.ai: one department's data</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Rows are checked before anything is saved; problems are shown row by row. A '*' marks a required column.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sections: one row per section (a group of students who always sit together).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab batches: how the section splits for labs, e.g. 'A1:30, A2:30' (name:students). Empty = whole section.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Teachers: one row per teacher of the department.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Name, Email (their login), Shifts (one or more shift names, comma separated), Max periods per day (default 5).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Subjects: one row per subject the department teaches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab equipment: what the lab room must have, e.g. computers. It must match a lab room's Equipment.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Can teach: which subjects each teacher can teach. Preference 1 = first choice, 2 = could also teach it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Used for teacher suggestions and to find a substitute when a teacher is on leave.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Classes: one row per class. Subject code, Sections (several separated by commas = one combined class),</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">  once that department's file is uploaded: upload Applied Sciences first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Rooms: rooms this department owns. Type: Lecture, Lab or Seminar. Seats. Equipment for labs.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shared halls (lecture theatres, seminar hall, drawing halls, workshops) are added by the College Admin in Setup.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rooms every department may use (e.g. a seminar hall) are added by the College Admin in Setup as shared rooms.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>rules and shared rooms. The College Admin sets those in Setup.</t>
         </is>

--- a/docs/demo-data/GNDEC/GNDEC_5_CE.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_5_CE.xlsx
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2611001@gndec.demo</t>
+          <t>2611001@gndec.test</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2611002@gndec.demo</t>
+          <t>2611002@gndec.test</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2611003@gndec.demo</t>
+          <t>2611003@gndec.test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2611004@gndec.demo</t>
+          <t>2611004@gndec.test</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2611005@gndec.demo</t>
+          <t>2611005@gndec.test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2611006@gndec.demo</t>
+          <t>2611006@gndec.test</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2611007@gndec.demo</t>
+          <t>2611007@gndec.test</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2611008@gndec.demo</t>
+          <t>2611008@gndec.test</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2611009@gndec.demo</t>
+          <t>2611009@gndec.test</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2611010@gndec.demo</t>
+          <t>2611010@gndec.test</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2611011@gndec.demo</t>
+          <t>2611011@gndec.test</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2611012@gndec.demo</t>
+          <t>2611012@gndec.test</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2611013@gndec.demo</t>
+          <t>2611013@gndec.test</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2611014@gndec.demo</t>
+          <t>2611014@gndec.test</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2611015@gndec.demo</t>
+          <t>2611015@gndec.test</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2611016@gndec.demo</t>
+          <t>2611016@gndec.test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2611017@gndec.demo</t>
+          <t>2611017@gndec.test</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2611018@gndec.demo</t>
+          <t>2611018@gndec.test</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2611019@gndec.demo</t>
+          <t>2611019@gndec.test</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2611020@gndec.demo</t>
+          <t>2611020@gndec.test</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2611021@gndec.demo</t>
+          <t>2611021@gndec.test</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2611022@gndec.demo</t>
+          <t>2611022@gndec.test</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2611023@gndec.demo</t>
+          <t>2611023@gndec.test</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2611024@gndec.demo</t>
+          <t>2611024@gndec.test</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2611025@gndec.demo</t>
+          <t>2611025@gndec.test</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2611026@gndec.demo</t>
+          <t>2611026@gndec.test</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2611027@gndec.demo</t>
+          <t>2611027@gndec.test</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2611028@gndec.demo</t>
+          <t>2611028@gndec.test</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2611029@gndec.demo</t>
+          <t>2611029@gndec.test</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2611030@gndec.demo</t>
+          <t>2611030@gndec.test</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2611031@gndec.demo</t>
+          <t>2611031@gndec.test</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2611032@gndec.demo</t>
+          <t>2611032@gndec.test</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2611033@gndec.demo</t>
+          <t>2611033@gndec.test</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2611034@gndec.demo</t>
+          <t>2611034@gndec.test</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2611035@gndec.demo</t>
+          <t>2611035@gndec.test</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2611036@gndec.demo</t>
+          <t>2611036@gndec.test</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2611037@gndec.demo</t>
+          <t>2611037@gndec.test</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2611038@gndec.demo</t>
+          <t>2611038@gndec.test</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2611039@gndec.demo</t>
+          <t>2611039@gndec.test</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2611040@gndec.demo</t>
+          <t>2611040@gndec.test</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2611041@gndec.demo</t>
+          <t>2611041@gndec.test</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2611042@gndec.demo</t>
+          <t>2611042@gndec.test</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2611043@gndec.demo</t>
+          <t>2611043@gndec.test</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2611044@gndec.demo</t>
+          <t>2611044@gndec.test</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2611045@gndec.demo</t>
+          <t>2611045@gndec.test</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2611046@gndec.demo</t>
+          <t>2611046@gndec.test</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2611047@gndec.demo</t>
+          <t>2611047@gndec.test</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2611048@gndec.demo</t>
+          <t>2611048@gndec.test</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2611049@gndec.demo</t>
+          <t>2611049@gndec.test</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2611050@gndec.demo</t>
+          <t>2611050@gndec.test</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2611051@gndec.demo</t>
+          <t>2611051@gndec.test</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2611052@gndec.demo</t>
+          <t>2611052@gndec.test</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2611053@gndec.demo</t>
+          <t>2611053@gndec.test</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2611054@gndec.demo</t>
+          <t>2611054@gndec.test</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2611055@gndec.demo</t>
+          <t>2611055@gndec.test</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2611056@gndec.demo</t>
+          <t>2611056@gndec.test</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2611057@gndec.demo</t>
+          <t>2611057@gndec.test</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2611058@gndec.demo</t>
+          <t>2611058@gndec.test</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2611059@gndec.demo</t>
+          <t>2611059@gndec.test</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2611060@gndec.demo</t>
+          <t>2611060@gndec.test</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2511001@gndec.demo</t>
+          <t>2511001@gndec.test</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2511002@gndec.demo</t>
+          <t>2511002@gndec.test</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2511003@gndec.demo</t>
+          <t>2511003@gndec.test</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2511004@gndec.demo</t>
+          <t>2511004@gndec.test</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2511005@gndec.demo</t>
+          <t>2511005@gndec.test</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2511006@gndec.demo</t>
+          <t>2511006@gndec.test</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2511007@gndec.demo</t>
+          <t>2511007@gndec.test</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2511008@gndec.demo</t>
+          <t>2511008@gndec.test</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2511009@gndec.demo</t>
+          <t>2511009@gndec.test</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2511010@gndec.demo</t>
+          <t>2511010@gndec.test</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2511011@gndec.demo</t>
+          <t>2511011@gndec.test</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2511012@gndec.demo</t>
+          <t>2511012@gndec.test</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2511013@gndec.demo</t>
+          <t>2511013@gndec.test</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2511014@gndec.demo</t>
+          <t>2511014@gndec.test</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2511015@gndec.demo</t>
+          <t>2511015@gndec.test</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2511016@gndec.demo</t>
+          <t>2511016@gndec.test</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2511017@gndec.demo</t>
+          <t>2511017@gndec.test</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2511018@gndec.demo</t>
+          <t>2511018@gndec.test</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2511019@gndec.demo</t>
+          <t>2511019@gndec.test</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2511020@gndec.demo</t>
+          <t>2511020@gndec.test</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2511021@gndec.demo</t>
+          <t>2511021@gndec.test</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2511022@gndec.demo</t>
+          <t>2511022@gndec.test</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2511023@gndec.demo</t>
+          <t>2511023@gndec.test</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2511024@gndec.demo</t>
+          <t>2511024@gndec.test</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2511025@gndec.demo</t>
+          <t>2511025@gndec.test</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2511026@gndec.demo</t>
+          <t>2511026@gndec.test</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2511027@gndec.demo</t>
+          <t>2511027@gndec.test</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2511028@gndec.demo</t>
+          <t>2511028@gndec.test</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2511029@gndec.demo</t>
+          <t>2511029@gndec.test</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2511030@gndec.demo</t>
+          <t>2511030@gndec.test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2511031@gndec.demo</t>
+          <t>2511031@gndec.test</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2511032@gndec.demo</t>
+          <t>2511032@gndec.test</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2511033@gndec.demo</t>
+          <t>2511033@gndec.test</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2511034@gndec.demo</t>
+          <t>2511034@gndec.test</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2511035@gndec.demo</t>
+          <t>2511035@gndec.test</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2511036@gndec.demo</t>
+          <t>2511036@gndec.test</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2511037@gndec.demo</t>
+          <t>2511037@gndec.test</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2511038@gndec.demo</t>
+          <t>2511038@gndec.test</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2511039@gndec.demo</t>
+          <t>2511039@gndec.test</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2511040@gndec.demo</t>
+          <t>2511040@gndec.test</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2511041@gndec.demo</t>
+          <t>2511041@gndec.test</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2511042@gndec.demo</t>
+          <t>2511042@gndec.test</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2511043@gndec.demo</t>
+          <t>2511043@gndec.test</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2511044@gndec.demo</t>
+          <t>2511044@gndec.test</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2511045@gndec.demo</t>
+          <t>2511045@gndec.test</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2511046@gndec.demo</t>
+          <t>2511046@gndec.test</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2511047@gndec.demo</t>
+          <t>2511047@gndec.test</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2511048@gndec.demo</t>
+          <t>2511048@gndec.test</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2511049@gndec.demo</t>
+          <t>2511049@gndec.test</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2511050@gndec.demo</t>
+          <t>2511050@gndec.test</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2511051@gndec.demo</t>
+          <t>2511051@gndec.test</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2511052@gndec.demo</t>
+          <t>2511052@gndec.test</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2511053@gndec.demo</t>
+          <t>2511053@gndec.test</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2511054@gndec.demo</t>
+          <t>2511054@gndec.test</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2511055@gndec.demo</t>
+          <t>2511055@gndec.test</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2511056@gndec.demo</t>
+          <t>2511056@gndec.test</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2511057@gndec.demo</t>
+          <t>2511057@gndec.test</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2511058@gndec.demo</t>
+          <t>2511058@gndec.test</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2511059@gndec.demo</t>
+          <t>2511059@gndec.test</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2511060@gndec.demo</t>
+          <t>2511060@gndec.test</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2511061@gndec.demo</t>
+          <t>2511061@gndec.test</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2511062@gndec.demo</t>
+          <t>2511062@gndec.test</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2511063@gndec.demo</t>
+          <t>2511063@gndec.test</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2511064@gndec.demo</t>
+          <t>2511064@gndec.test</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2511065@gndec.demo</t>
+          <t>2511065@gndec.test</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2511066@gndec.demo</t>
+          <t>2511066@gndec.test</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2511067@gndec.demo</t>
+          <t>2511067@gndec.test</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2511068@gndec.demo</t>
+          <t>2511068@gndec.test</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2511069@gndec.demo</t>
+          <t>2511069@gndec.test</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2511070@gndec.demo</t>
+          <t>2511070@gndec.test</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2511071@gndec.demo</t>
+          <t>2511071@gndec.test</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2511072@gndec.demo</t>
+          <t>2511072@gndec.test</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2511073@gndec.demo</t>
+          <t>2511073@gndec.test</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2511074@gndec.demo</t>
+          <t>2511074@gndec.test</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2511075@gndec.demo</t>
+          <t>2511075@gndec.test</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2511076@gndec.demo</t>
+          <t>2511076@gndec.test</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2511077@gndec.demo</t>
+          <t>2511077@gndec.test</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2511078@gndec.demo</t>
+          <t>2511078@gndec.test</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2511079@gndec.demo</t>
+          <t>2511079@gndec.test</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2511080@gndec.demo</t>
+          <t>2511080@gndec.test</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2511081@gndec.demo</t>
+          <t>2511081@gndec.test</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2511082@gndec.demo</t>
+          <t>2511082@gndec.test</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2511083@gndec.demo</t>
+          <t>2511083@gndec.test</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2511084@gndec.demo</t>
+          <t>2511084@gndec.test</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2511085@gndec.demo</t>
+          <t>2511085@gndec.test</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2511086@gndec.demo</t>
+          <t>2511086@gndec.test</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2511087@gndec.demo</t>
+          <t>2511087@gndec.test</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2511088@gndec.demo</t>
+          <t>2511088@gndec.test</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2511089@gndec.demo</t>
+          <t>2511089@gndec.test</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2511090@gndec.demo</t>
+          <t>2511090@gndec.test</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2511091@gndec.demo</t>
+          <t>2511091@gndec.test</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2511092@gndec.demo</t>
+          <t>2511092@gndec.test</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2511093@gndec.demo</t>
+          <t>2511093@gndec.test</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2511094@gndec.demo</t>
+          <t>2511094@gndec.test</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2511095@gndec.demo</t>
+          <t>2511095@gndec.test</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2511096@gndec.demo</t>
+          <t>2511096@gndec.test</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2511097@gndec.demo</t>
+          <t>2511097@gndec.test</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2511098@gndec.demo</t>
+          <t>2511098@gndec.test</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2511099@gndec.demo</t>
+          <t>2511099@gndec.test</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2511100@gndec.demo</t>
+          <t>2511100@gndec.test</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2511101@gndec.demo</t>
+          <t>2511101@gndec.test</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2511102@gndec.demo</t>
+          <t>2511102@gndec.test</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2511103@gndec.demo</t>
+          <t>2511103@gndec.test</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2511104@gndec.demo</t>
+          <t>2511104@gndec.test</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2511105@gndec.demo</t>
+          <t>2511105@gndec.test</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2511106@gndec.demo</t>
+          <t>2511106@gndec.test</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2511107@gndec.demo</t>
+          <t>2511107@gndec.test</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2511108@gndec.demo</t>
+          <t>2511108@gndec.test</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2511109@gndec.demo</t>
+          <t>2511109@gndec.test</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2511110@gndec.demo</t>
+          <t>2511110@gndec.test</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2511111@gndec.demo</t>
+          <t>2511111@gndec.test</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2511112@gndec.demo</t>
+          <t>2511112@gndec.test</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2511113@gndec.demo</t>
+          <t>2511113@gndec.test</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2511114@gndec.demo</t>
+          <t>2511114@gndec.test</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2511115@gndec.demo</t>
+          <t>2511115@gndec.test</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2511116@gndec.demo</t>
+          <t>2511116@gndec.test</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2511117@gndec.demo</t>
+          <t>2511117@gndec.test</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2511118@gndec.demo</t>
+          <t>2511118@gndec.test</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2411001@gndec.demo</t>
+          <t>2411001@gndec.test</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2411002@gndec.demo</t>
+          <t>2411002@gndec.test</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2411003@gndec.demo</t>
+          <t>2411003@gndec.test</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2411004@gndec.demo</t>
+          <t>2411004@gndec.test</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2411005@gndec.demo</t>
+          <t>2411005@gndec.test</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2411006@gndec.demo</t>
+          <t>2411006@gndec.test</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2411007@gndec.demo</t>
+          <t>2411007@gndec.test</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2411008@gndec.demo</t>
+          <t>2411008@gndec.test</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2411009@gndec.demo</t>
+          <t>2411009@gndec.test</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2411010@gndec.demo</t>
+          <t>2411010@gndec.test</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2411011@gndec.demo</t>
+          <t>2411011@gndec.test</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2411012@gndec.demo</t>
+          <t>2411012@gndec.test</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2411013@gndec.demo</t>
+          <t>2411013@gndec.test</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2411014@gndec.demo</t>
+          <t>2411014@gndec.test</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2411015@gndec.demo</t>
+          <t>2411015@gndec.test</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2411016@gndec.demo</t>
+          <t>2411016@gndec.test</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2411017@gndec.demo</t>
+          <t>2411017@gndec.test</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2411018@gndec.demo</t>
+          <t>2411018@gndec.test</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2411019@gndec.demo</t>
+          <t>2411019@gndec.test</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2411020@gndec.demo</t>
+          <t>2411020@gndec.test</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2411021@gndec.demo</t>
+          <t>2411021@gndec.test</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2411022@gndec.demo</t>
+          <t>2411022@gndec.test</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2411023@gndec.demo</t>
+          <t>2411023@gndec.test</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2411024@gndec.demo</t>
+          <t>2411024@gndec.test</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2411025@gndec.demo</t>
+          <t>2411025@gndec.test</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2411026@gndec.demo</t>
+          <t>2411026@gndec.test</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2411027@gndec.demo</t>
+          <t>2411027@gndec.test</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2411028@gndec.demo</t>
+          <t>2411028@gndec.test</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2411029@gndec.demo</t>
+          <t>2411029@gndec.test</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2411030@gndec.demo</t>
+          <t>2411030@gndec.test</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2411031@gndec.demo</t>
+          <t>2411031@gndec.test</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2411032@gndec.demo</t>
+          <t>2411032@gndec.test</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2411033@gndec.demo</t>
+          <t>2411033@gndec.test</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2411034@gndec.demo</t>
+          <t>2411034@gndec.test</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2411035@gndec.demo</t>
+          <t>2411035@gndec.test</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2411036@gndec.demo</t>
+          <t>2411036@gndec.test</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2411037@gndec.demo</t>
+          <t>2411037@gndec.test</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2411038@gndec.demo</t>
+          <t>2411038@gndec.test</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2411039@gndec.demo</t>
+          <t>2411039@gndec.test</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2411040@gndec.demo</t>
+          <t>2411040@gndec.test</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2411041@gndec.demo</t>
+          <t>2411041@gndec.test</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2411042@gndec.demo</t>
+          <t>2411042@gndec.test</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2411043@gndec.demo</t>
+          <t>2411043@gndec.test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2411044@gndec.demo</t>
+          <t>2411044@gndec.test</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2411045@gndec.demo</t>
+          <t>2411045@gndec.test</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2411046@gndec.demo</t>
+          <t>2411046@gndec.test</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2411047@gndec.demo</t>
+          <t>2411047@gndec.test</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2411048@gndec.demo</t>
+          <t>2411048@gndec.test</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2411049@gndec.demo</t>
+          <t>2411049@gndec.test</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2411050@gndec.demo</t>
+          <t>2411050@gndec.test</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2411051@gndec.demo</t>
+          <t>2411051@gndec.test</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2411052@gndec.demo</t>
+          <t>2411052@gndec.test</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2411053@gndec.demo</t>
+          <t>2411053@gndec.test</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2411054@gndec.demo</t>
+          <t>2411054@gndec.test</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2411055@gndec.demo</t>
+          <t>2411055@gndec.test</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2411056@gndec.demo</t>
+          <t>2411056@gndec.test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2411057@gndec.demo</t>
+          <t>2411057@gndec.test</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2411058@gndec.demo</t>
+          <t>2411058@gndec.test</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2411059@gndec.demo</t>
+          <t>2411059@gndec.test</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2411060@gndec.demo</t>
+          <t>2411060@gndec.test</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2311001@gndec.demo</t>
+          <t>2311001@gndec.test</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2311002@gndec.demo</t>
+          <t>2311002@gndec.test</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2311003@gndec.demo</t>
+          <t>2311003@gndec.test</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2311004@gndec.demo</t>
+          <t>2311004@gndec.test</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2311005@gndec.demo</t>
+          <t>2311005@gndec.test</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2311006@gndec.demo</t>
+          <t>2311006@gndec.test</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2311007@gndec.demo</t>
+          <t>2311007@gndec.test</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2311008@gndec.demo</t>
+          <t>2311008@gndec.test</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2311009@gndec.demo</t>
+          <t>2311009@gndec.test</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2311010@gndec.demo</t>
+          <t>2311010@gndec.test</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2311011@gndec.demo</t>
+          <t>2311011@gndec.test</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2311012@gndec.demo</t>
+          <t>2311012@gndec.test</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2311013@gndec.demo</t>
+          <t>2311013@gndec.test</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2311014@gndec.demo</t>
+          <t>2311014@gndec.test</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2311015@gndec.demo</t>
+          <t>2311015@gndec.test</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2311016@gndec.demo</t>
+          <t>2311016@gndec.test</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2311017@gndec.demo</t>
+          <t>2311017@gndec.test</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2311018@gndec.demo</t>
+          <t>2311018@gndec.test</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2311019@gndec.demo</t>
+          <t>2311019@gndec.test</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2311020@gndec.demo</t>
+          <t>2311020@gndec.test</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2311021@gndec.demo</t>
+          <t>2311021@gndec.test</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2311022@gndec.demo</t>
+          <t>2311022@gndec.test</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2311023@gndec.demo</t>
+          <t>2311023@gndec.test</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2311024@gndec.demo</t>
+          <t>2311024@gndec.test</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2311025@gndec.demo</t>
+          <t>2311025@gndec.test</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2311026@gndec.demo</t>
+          <t>2311026@gndec.test</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2311027@gndec.demo</t>
+          <t>2311027@gndec.test</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2311028@gndec.demo</t>
+          <t>2311028@gndec.test</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2311029@gndec.demo</t>
+          <t>2311029@gndec.test</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2311030@gndec.demo</t>
+          <t>2311030@gndec.test</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2311031@gndec.demo</t>
+          <t>2311031@gndec.test</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2311032@gndec.demo</t>
+          <t>2311032@gndec.test</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2311033@gndec.demo</t>
+          <t>2311033@gndec.test</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2311034@gndec.demo</t>
+          <t>2311034@gndec.test</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2311035@gndec.demo</t>
+          <t>2311035@gndec.test</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2311036@gndec.demo</t>
+          <t>2311036@gndec.test</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2311037@gndec.demo</t>
+          <t>2311037@gndec.test</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2311038@gndec.demo</t>
+          <t>2311038@gndec.test</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2311039@gndec.demo</t>
+          <t>2311039@gndec.test</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2311040@gndec.demo</t>
+          <t>2311040@gndec.test</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2311041@gndec.demo</t>
+          <t>2311041@gndec.test</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2311042@gndec.demo</t>
+          <t>2311042@gndec.test</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2311043@gndec.demo</t>
+          <t>2311043@gndec.test</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2311044@gndec.demo</t>
+          <t>2311044@gndec.test</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2311045@gndec.demo</t>
+          <t>2311045@gndec.test</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2311046@gndec.demo</t>
+          <t>2311046@gndec.test</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2311047@gndec.demo</t>
+          <t>2311047@gndec.test</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2311048@gndec.demo</t>
+          <t>2311048@gndec.test</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2311049@gndec.demo</t>
+          <t>2311049@gndec.test</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2311050@gndec.demo</t>
+          <t>2311050@gndec.test</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2311051@gndec.demo</t>
+          <t>2311051@gndec.test</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2311052@gndec.demo</t>
+          <t>2311052@gndec.test</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2311053@gndec.demo</t>
+          <t>2311053@gndec.test</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2311054@gndec.demo</t>
+          <t>2311054@gndec.test</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2311055@gndec.demo</t>
+          <t>2311055@gndec.test</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2311056@gndec.demo</t>
+          <t>2311056@gndec.test</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2311057@gndec.demo</t>
+          <t>2311057@gndec.test</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2311058@gndec.demo</t>
+          <t>2311058@gndec.test</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2311059@gndec.demo</t>
+          <t>2311059@gndec.test</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2311060@gndec.demo</t>
+          <t>2311060@gndec.test</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
